--- a/Master/2362r00/2362r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/2362r00/2362r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1054,322 +1054,402 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>5.127</v>
+        <v>3.243</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>4.2936</v>
+        <v>4.2914</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.7241</v>
+        <v>-2.8904</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>0.0253</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>2.128</v>
+        <v>5.245</v>
       </c>
       <c r="B32" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="D32" s="7" t="n">
-        <v>4.3569</v>
+        <v>4.2914</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>-0.9169</v>
+        <v>-3.0573</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0.0117</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>1.129</v>
+        <v>4.242</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>4.4318</v>
+        <v>4.2916</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-1.1268</v>
+        <v>-2.6799</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>4.13</v>
+        <v>1.241</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>4.487</v>
+        <v>4.2924</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>-1.0731</v>
+        <v>-2.7137</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.0104</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>3.131</v>
+        <v>5.127</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4.5479</v>
+        <v>4.2936</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-1.2871</v>
+        <v>-0.7241</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0.0175</v>
+        <v>0.0253</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>6.132</v>
+        <v>2.128</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>4.597</v>
+        <v>4.3569</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>-1.2475</v>
+        <v>-0.9169</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.008</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>5.133</v>
+        <v>1.129</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>4.6414</v>
+        <v>4.4318</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-1.4597</v>
+        <v>-1.1268</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.0137</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>2.134</v>
+        <v>4.13</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>4.6824</v>
+        <v>4.487</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>-1.6822</v>
+        <v>-1.0731</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.0059</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>1.135</v>
+        <v>3.131</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>4.7113</v>
+        <v>4.5479</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-1.8862</v>
+        <v>-1.2871</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.0097</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>4.136</v>
+        <v>6.132</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>4.7424</v>
+        <v>4.597</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>-1.8648</v>
+        <v>-1.2475</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.0042</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>3.137</v>
+        <v>5.133</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>4.7586</v>
+        <v>4.6414</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-2.0555</v>
+        <v>-1.4597</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.0058</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>6.138</v>
+        <v>2.134</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>4.7792</v>
+        <v>4.6824</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>-2.0572</v>
+        <v>-1.6822</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.002</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>5.139</v>
+        <v>1.135</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>4.7822</v>
+        <v>4.7113</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-2.2211</v>
+        <v>-1.8862</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.0026</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>1.141</v>
+        <v>4.136</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>4.7988</v>
+        <v>4.7424</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>-2.6138</v>
+        <v>-1.8648</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.0022</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
+        <v>3.137</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>4.7586</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>-2.0555</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0.0058</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>6.138</v>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>4.7792</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>-2.0572</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>5.139</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>4.7822</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>-2.2211</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0.0026</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>4.7988</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>-2.6138</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>0.0022</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
         <v>2.14</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B49" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="7" t="n">
+      <c r="C49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="7" t="n">
         <v>4.8016</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E49" s="7" t="n">
         <v>-2.483</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F49" s="7" t="n">
         <v>0.0035</v>
       </c>
     </row>
-    <row r="47">
-      <c r="E47" s="8" t="inlineStr">
+    <row r="51">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F47" s="9" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="E48" s="8" t="inlineStr">
+      <c r="F51" s="9" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>1.1937</v>
+      <c r="F52" s="10" t="n">
+        <v>1.1954</v>
       </c>
     </row>
   </sheetData>
